--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944447C6-4A39-4504-8202-10E4218DD590}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5E96330-572C-4909-B4CA-04FF892765B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,42 @@
   </si>
   <si>
     <t>today DBMS CA2</t>
+  </si>
+  <si>
+    <t>today start lpu protest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today fell very bad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack bag </t>
+  </si>
+  <si>
+    <t>travel to a village</t>
+  </si>
+  <si>
+    <t>I was on the train today</t>
+  </si>
+  <si>
+    <t>I was viste agriculture land today</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> preparation for exam today</t>
+  </si>
+  <si>
+    <t>today strat online classes</t>
+  </si>
+  <si>
+    <t>attend online class</t>
+  </si>
+  <si>
+    <t>today online class</t>
+  </si>
+  <si>
+    <t>doubt classes</t>
+  </si>
+  <si>
+    <t>doubt clearing</t>
   </si>
 </sst>
 </file>
@@ -559,6 +595,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2852,312 +2892,648 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B45" s="14">
+        <v>450</v>
+      </c>
+      <c r="C45" s="14">
+        <v>40</v>
+      </c>
+      <c r="D45" s="14">
+        <v>350</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>350</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>450</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B47" s="14">
+        <v>450</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>350</v>
+      </c>
+      <c r="E47" s="14">
+        <v>140</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>260</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>40</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>300</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>300</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B50" s="14">
+        <v>600</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B51" s="14">
+        <v>720</v>
+      </c>
+      <c r="C51" s="14">
+        <v>50</v>
+      </c>
+      <c r="D51" s="14">
+        <v>150</v>
+      </c>
+      <c r="E51" s="14">
+        <v>50</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>400</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B52" s="14">
+        <v>750</v>
+      </c>
+      <c r="C52" s="14">
+        <v>40</v>
+      </c>
+      <c r="D52" s="14">
+        <v>260</v>
+      </c>
+      <c r="E52" s="14">
+        <v>180</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B53" s="14">
+        <v>700</v>
+      </c>
+      <c r="C53" s="14">
+        <v>60</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>100</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>150</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B54" s="14">
+        <v>740</v>
+      </c>
+      <c r="C54" s="14">
+        <v>50</v>
+      </c>
+      <c r="D54" s="14">
+        <v>200</v>
+      </c>
+      <c r="E54" s="14">
+        <v>180</v>
+      </c>
+      <c r="F54" s="14">
+        <v>100</v>
+      </c>
+      <c r="G54" s="14">
+        <v>2</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B55" s="14">
+        <v>730</v>
+      </c>
+      <c r="C55" s="14">
+        <v>40</v>
+      </c>
+      <c r="D55" s="14">
+        <v>90</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>350</v>
+      </c>
+      <c r="G55" s="14">
+        <v>7</v>
+      </c>
+      <c r="H55" s="14">
+        <v>140</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>44111</v>
+      </c>
+      <c r="B56" s="14">
+        <v>720</v>
+      </c>
+      <c r="C56" s="14">
+        <v>50</v>
+      </c>
+      <c r="D56" s="14">
+        <v>150</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>200</v>
+      </c>
+      <c r="G56" s="14">
+        <v>4</v>
+      </c>
+      <c r="H56" s="14">
+        <v>150</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>44112</v>
+      </c>
+      <c r="B57" s="14">
+        <v>720</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>120</v>
+      </c>
+      <c r="E57" s="14">
+        <v>50</v>
+      </c>
+      <c r="F57" s="14">
+        <v>350</v>
+      </c>
+      <c r="G57" s="14">
+        <v>7</v>
+      </c>
+      <c r="H57" s="14">
+        <v>130</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B58" s="14">
+        <v>720</v>
+      </c>
+      <c r="C58" s="14">
+        <v>50</v>
+      </c>
+      <c r="D58" s="14">
+        <v>60</v>
+      </c>
+      <c r="E58" s="14">
+        <v>30</v>
+      </c>
+      <c r="F58" s="14">
+        <v>350</v>
+      </c>
+      <c r="G58" s="14">
+        <v>7</v>
+      </c>
+      <c r="H58" s="14">
+        <v>150</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5E96330-572C-4909-B4CA-04FF892765B3}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{738ED92D-DA85-42B9-81F2-F789E53CEB8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,7 +313,7 @@
     <t>doubt classes</t>
   </si>
   <si>
-    <t>doubt clearing</t>
+    <t xml:space="preserve"> clearing all doubt</t>
   </si>
 </sst>
 </file>
@@ -3536,26 +3536,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B59" s="14">
+        <v>720</v>
+      </c>
+      <c r="C59" s="14">
+        <v>50</v>
+      </c>
+      <c r="D59" s="14">
+        <v>180</v>
+      </c>
+      <c r="E59" s="14">
+        <v>90</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>140</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{738ED92D-DA85-42B9-81F2-F789E53CEB8E}"/>
+  <xr:revisionPtr revIDLastSave="572" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1937E8EC-A6D7-4E88-A1AF-90D80353F797}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t xml:space="preserve"> clearing all doubt</t>
+  </si>
+  <si>
+    <t>Good Day</t>
   </si>
 </sst>
 </file>
@@ -3582,70 +3585,142 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B60" s="14">
+        <v>740</v>
+      </c>
+      <c r="C60" s="14">
+        <v>65</v>
+      </c>
+      <c r="D60" s="14">
+        <v>250</v>
+      </c>
+      <c r="E60" s="14">
+        <v>120</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>150</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B61" s="14">
+        <v>720</v>
+      </c>
+      <c r="C61" s="14">
+        <v>45</v>
+      </c>
+      <c r="D61" s="14">
+        <v>220</v>
+      </c>
+      <c r="E61" s="14">
+        <v>150</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>260</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B62" s="14">
+        <v>750</v>
+      </c>
+      <c r="C62" s="14">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14">
+        <v>180</v>
+      </c>
+      <c r="E62" s="14">
+        <v>120</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>150</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="572" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1937E8EC-A6D7-4E88-A1AF-90D80353F797}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9D485DB-6F4B-4289-951F-A6B62E3FCCFB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>Good Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-10-15</t>
   </si>
 </sst>
 </file>
@@ -3723,92 +3726,188 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+      <c r="A63" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B63" s="14">
+        <v>720</v>
+      </c>
+      <c r="C63" s="14">
+        <v>50</v>
+      </c>
+      <c r="D63" s="14">
+        <v>180</v>
+      </c>
+      <c r="E63" s="14">
+        <v>90</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>140</v>
+      </c>
+      <c r="I63" s="15">
+        <f t="shared" ref="I63:I66" si="8">IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
+        <v>1180</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" ref="J63:J66" si="9">IF(I63="","",1440-I63)</f>
+        <v>260</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+      <c r="A64" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" s="14">
+        <v>740</v>
+      </c>
+      <c r="C64" s="14">
+        <v>65</v>
+      </c>
+      <c r="D64" s="14">
+        <v>250</v>
+      </c>
+      <c r="E64" s="14">
+        <v>120</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>150</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" si="8"/>
+        <v>1325</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="9"/>
+        <v>115</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+      <c r="A65" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B65" s="14">
+        <v>720</v>
+      </c>
+      <c r="C65" s="14">
+        <v>45</v>
+      </c>
+      <c r="D65" s="14">
+        <v>220</v>
+      </c>
+      <c r="E65" s="14">
+        <v>150</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>260</v>
+      </c>
+      <c r="I65" s="15">
+        <f t="shared" si="8"/>
+        <v>1395</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+      <c r="A66" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B66" s="14">
+        <v>750</v>
+      </c>
+      <c r="C66" s="14">
+        <v>60</v>
+      </c>
+      <c r="D66" s="14">
+        <v>180</v>
+      </c>
+      <c r="E66" s="14">
+        <v>120</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>150</v>
+      </c>
+      <c r="I66" s="15">
+        <f t="shared" si="8"/>
+        <v>1260</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" si="9"/>
+        <v>180</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
@@ -3886,11 +3985,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3908,11 +4007,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3930,11 +4029,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3952,11 +4051,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3974,11 +4073,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3996,11 +4095,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -4018,11 +4117,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4040,11 +4139,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -4062,11 +4161,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -4084,11 +4183,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -4106,11 +4205,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -4128,11 +4227,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -4150,11 +4249,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -4172,11 +4271,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4194,11 +4293,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4216,11 +4315,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4238,11 +4337,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4260,11 +4359,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4282,11 +4381,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4304,11 +4403,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4326,11 +4425,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4348,11 +4447,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4370,11 +4469,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4392,11 +4491,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4414,11 +4513,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4436,11 +4535,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4458,11 +4557,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4480,11 +4579,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4502,11 +4601,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4524,11 +4623,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4546,11 +4645,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4568,11 +4667,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4590,11 +4689,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4612,11 +4711,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4634,11 +4733,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4656,11 +4755,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4678,11 +4777,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4700,11 +4799,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4722,11 +4821,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4744,11 +4843,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4766,11 +4865,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4788,11 +4887,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4810,11 +4909,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4832,11 +4931,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4854,11 +4953,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4876,11 +4975,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4898,11 +4997,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4920,11 +5019,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4942,11 +5041,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4964,11 +5063,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4986,11 +5085,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -5008,11 +5107,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -5030,11 +5129,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -5052,11 +5151,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -5074,11 +5173,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5096,11 +5195,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5118,11 +5217,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5140,11 +5239,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5162,11 +5261,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5184,11 +5283,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5206,11 +5305,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5228,11 +5327,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5250,11 +5349,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5272,11 +5371,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5294,11 +5393,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5316,11 +5415,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5338,11 +5437,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5360,11 +5459,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5382,11 +5481,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5404,11 +5503,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5426,11 +5525,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5448,11 +5547,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5470,11 +5569,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5492,11 +5591,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5514,11 +5613,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5536,11 +5635,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5558,11 +5657,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5580,11 +5679,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5602,11 +5701,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5624,11 +5723,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5646,11 +5745,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5668,11 +5767,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5690,11 +5789,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5712,11 +5811,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5734,11 +5833,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5756,11 +5855,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5778,11 +5877,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5800,11 +5899,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5822,11 +5921,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5844,11 +5943,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5866,11 +5965,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5888,11 +5987,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5910,11 +6009,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5932,11 +6031,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5954,11 +6053,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5976,11 +6075,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5998,11 +6097,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6020,11 +6119,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6042,11 +6141,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6064,11 +6163,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6086,11 +6185,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6108,11 +6207,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6130,11 +6229,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6152,11 +6251,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6174,11 +6273,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6196,11 +6295,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6218,11 +6317,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6240,11 +6339,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6262,11 +6361,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6284,11 +6383,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6306,11 +6405,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6328,11 +6427,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6350,11 +6449,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6372,11 +6471,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6394,11 +6493,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6416,11 +6515,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6438,11 +6537,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6460,11 +6559,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6482,11 +6581,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6504,11 +6603,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6526,11 +6625,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6548,11 +6647,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6570,11 +6669,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6592,11 +6691,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6614,11 +6713,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6636,11 +6735,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6658,11 +6757,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6680,11 +6779,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6702,11 +6801,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6724,11 +6823,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6746,11 +6845,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6768,11 +6867,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6790,11 +6889,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6812,11 +6911,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6834,11 +6933,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6856,11 +6955,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6878,11 +6977,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6900,11 +6999,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6922,11 +7021,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6944,11 +7043,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6966,11 +7065,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6988,11 +7087,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7010,11 +7109,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7032,11 +7131,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7054,11 +7153,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7076,11 +7175,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7098,11 +7197,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7120,11 +7219,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7142,11 +7241,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7164,11 +7263,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7186,11 +7285,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7208,11 +7307,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7230,11 +7329,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7252,11 +7351,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7274,11 +7373,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7296,11 +7395,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7318,11 +7417,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7340,11 +7439,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7362,11 +7461,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7384,11 +7483,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7406,11 +7505,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7428,11 +7527,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7450,11 +7549,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7472,11 +7571,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7494,11 +7593,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7516,11 +7615,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7538,11 +7637,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7560,11 +7659,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7582,11 +7681,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7604,11 +7703,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7626,11 +7725,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7648,11 +7747,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7670,11 +7769,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7692,11 +7791,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7714,11 +7813,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7736,11 +7835,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7758,11 +7857,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7780,11 +7879,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7802,11 +7901,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7824,11 +7923,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7846,11 +7945,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7868,11 +7967,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7890,11 +7989,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7912,11 +8011,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7934,11 +8033,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7956,11 +8055,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7978,11 +8077,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8000,11 +8099,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8022,11 +8121,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8044,11 +8143,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8066,11 +8165,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8088,11 +8187,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8110,11 +8209,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8132,11 +8231,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8154,11 +8253,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8176,11 +8275,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8198,11 +8297,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8220,11 +8319,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8242,11 +8341,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8264,11 +8363,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8286,11 +8385,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8308,11 +8407,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8330,11 +8429,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8352,11 +8451,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8374,11 +8473,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8396,11 +8495,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8418,11 +8517,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8440,11 +8539,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8462,11 +8561,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8484,11 +8583,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8506,11 +8605,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8528,11 +8627,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8550,11 +8649,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8572,11 +8671,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8594,11 +8693,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8616,11 +8715,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8638,11 +8737,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8660,11 +8759,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8682,11 +8781,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8704,11 +8803,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8726,11 +8825,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8748,11 +8847,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8770,11 +8869,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8792,11 +8891,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8814,11 +8913,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8836,11 +8935,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8858,11 +8957,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8880,11 +8979,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8902,11 +9001,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8924,11 +9023,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8946,11 +9045,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8968,11 +9067,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8990,11 +9089,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9012,11 +9111,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9034,11 +9133,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9056,11 +9155,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9078,11 +9177,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9100,11 +9199,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9122,11 +9221,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9144,11 +9243,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9166,11 +9265,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9188,11 +9287,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9210,11 +9309,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9232,11 +9331,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9254,11 +9353,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9276,11 +9375,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9298,11 +9397,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9320,11 +9419,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9342,11 +9441,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9364,11 +9463,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9386,11 +9485,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9408,11 +9507,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9430,11 +9529,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9452,11 +9551,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9474,11 +9573,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9496,11 +9595,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9518,11 +9617,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9540,11 +9639,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9562,11 +9661,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9584,11 +9683,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9606,11 +9705,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9628,11 +9727,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9650,11 +9749,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9672,11 +9771,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9694,11 +9793,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9716,11 +9815,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9738,11 +9837,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9760,11 +9859,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9782,11 +9881,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9804,11 +9903,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9826,11 +9925,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9848,11 +9947,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9870,11 +9969,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9892,11 +9991,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9914,11 +10013,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9936,11 +10035,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9958,11 +10057,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9980,11 +10079,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10002,11 +10101,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10024,11 +10123,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10046,11 +10145,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10068,11 +10167,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10090,11 +10189,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10112,11 +10211,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10134,11 +10233,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10156,11 +10255,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10178,11 +10277,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10200,11 +10299,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10222,11 +10321,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10244,11 +10343,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10266,11 +10365,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10288,11 +10387,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10310,11 +10409,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10332,11 +10431,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10354,11 +10453,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10376,11 +10475,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10398,11 +10497,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10420,11 +10519,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10442,11 +10541,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10464,11 +10563,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10486,11 +10585,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10508,11 +10607,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10530,11 +10629,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10552,11 +10651,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10574,11 +10673,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10596,11 +10695,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10618,11 +10717,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10640,11 +10739,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10662,11 +10761,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10684,11 +10783,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10706,11 +10805,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10728,11 +10827,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10750,11 +10849,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10772,11 +10871,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10794,11 +10893,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10816,11 +10915,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10838,11 +10937,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10860,11 +10959,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10882,11 +10981,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10904,11 +11003,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10926,11 +11025,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10948,11 +11047,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10970,11 +11069,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10992,11 +11091,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11014,11 +11113,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11036,11 +11135,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11058,11 +11157,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11080,11 +11179,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11102,11 +11201,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11124,11 +11223,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11146,11 +11245,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11168,11 +11267,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9D485DB-6F4B-4289-951F-A6B62E3FCCFB}"/>
+  <xr:revisionPtr revIDLastSave="581" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F50BDF-F027-4600-8BFD-4EE98BB4B87B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,21 @@
   </si>
   <si>
     <t xml:space="preserve"> 2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-10-16</t>
+  </si>
+  <si>
+    <t>to prepration for exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> exam preprations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> today back for LPU</t>
   </si>
 </sst>
 </file>
@@ -3811,15 +3826,15 @@
         <v>50</v>
       </c>
       <c r="M64" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N64" s="17" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13">
-        <v>46307</v>
+      <c r="A65" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="B65" s="14">
         <v>720</v>
@@ -3860,12 +3875,12 @@
         <v>55</v>
       </c>
       <c r="N65" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13">
-        <v>46308</v>
+      <c r="A66" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="B66" s="14">
         <v>750</v>
@@ -3906,7 +3921,7 @@
         <v>51</v>
       </c>
       <c r="N66" s="17" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="581" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F50BDF-F027-4600-8BFD-4EE98BB4B87B}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{601C8EB6-D4AA-43A4-A5D4-E37CA0895BE2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t xml:space="preserve"> today back for LPU</t>
+  </si>
+  <si>
+    <t>today I am on train</t>
   </si>
 </sst>
 </file>
@@ -3925,26 +3928,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="14">
+        <v>850</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>180</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>200</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="594" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{601C8EB6-D4AA-43A4-A5D4-E37CA0895BE2}"/>
+  <xr:revisionPtr revIDLastSave="607" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69808B2C-1938-4597-B778-C40F4539753C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3961,7 +3961,7 @@
         <v>210</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L67" s="16" t="s">
         <v>56</v>
@@ -3974,26 +3974,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="14">
+        <v>820</v>
+      </c>
+      <c r="C68" s="14">
+        <v>20</v>
+      </c>
+      <c r="D68" s="14">
+        <v>150</v>
+      </c>
+      <c r="E68" s="14">
+        <v>20</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>240</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="607" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69808B2C-1938-4597-B778-C40F4539753C}"/>
+  <xr:revisionPtr revIDLastSave="632" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFB609E-8D18-4CA9-9668-E81644817547}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>today I am on train</t>
+  </si>
+  <si>
+    <t>today start class after midterm</t>
   </si>
 </sst>
 </file>
@@ -4020,48 +4023,96 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="14">
+        <v>700</v>
+      </c>
+      <c r="C69" s="14">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14">
+        <v>250</v>
+      </c>
+      <c r="E69" s="14">
+        <v>150</v>
+      </c>
+      <c r="F69" s="14">
+        <v>2</v>
+      </c>
+      <c r="G69" s="14">
+        <v>100</v>
+      </c>
+      <c r="H69" s="14">
+        <v>245</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1377</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="14">
+        <v>720</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="14">
+        <v>350</v>
+      </c>
+      <c r="E70" s="14">
+        <v>120</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>180</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="632" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFB609E-8D18-4CA9-9668-E81644817547}"/>
+  <xr:revisionPtr revIDLastSave="646" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E0D4844-EF62-4174-A831-BD8238A5063B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4115,26 +4115,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="14">
+        <v>700</v>
+      </c>
+      <c r="C71" s="14">
+        <v>30</v>
+      </c>
+      <c r="D71" s="14">
+        <v>140</v>
+      </c>
+      <c r="E71" s="14">
+        <v>70</v>
+      </c>
+      <c r="F71" s="14">
+        <v>200</v>
+      </c>
+      <c r="G71" s="14">
+        <v>4</v>
+      </c>
+      <c r="H71" s="14">
+        <v>230</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="646" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E0D4844-EF62-4174-A831-BD8238A5063B}"/>
+  <xr:revisionPtr revIDLastSave="663" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F87C6E8F-CB0A-4326-B859-8630B383D0F9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4039,21 +4039,21 @@
         <v>150</v>
       </c>
       <c r="F69" s="14">
+        <v>100</v>
+      </c>
+      <c r="G69" s="14">
         <v>2</v>
       </c>
-      <c r="G69" s="14">
-        <v>100</v>
-      </c>
       <c r="H69" s="14">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K69" s="16" t="s">
         <v>64</v>
@@ -4161,26 +4161,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="14">
+        <v>740</v>
+      </c>
+      <c r="C72" s="14">
+        <v>39</v>
+      </c>
+      <c r="D72" s="14">
+        <v>90</v>
+      </c>
+      <c r="E72" s="14">
+        <v>80</v>
+      </c>
+      <c r="F72" s="14">
+        <v>350</v>
+      </c>
+      <c r="G72" s="14">
+        <v>7</v>
+      </c>
+      <c r="H72" s="14">
+        <v>100</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1399</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>41</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="663" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F87C6E8F-CB0A-4326-B859-8630B383D0F9}"/>
+  <xr:revisionPtr revIDLastSave="675" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB7210C-A999-4769-96E6-57B0CE6404B4}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>today start class after midterm</t>
+  </si>
+  <si>
+    <t>today learn join in DBMS</t>
   </si>
 </sst>
 </file>
@@ -4207,26 +4210,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="14">
+        <v>700</v>
+      </c>
+      <c r="C73" s="14">
+        <v>20</v>
+      </c>
+      <c r="D73" s="14">
+        <v>120</v>
+      </c>
+      <c r="E73" s="14">
+        <v>60</v>
+      </c>
+      <c r="F73" s="14">
+        <v>350</v>
+      </c>
+      <c r="G73" s="14">
+        <v>7</v>
+      </c>
+      <c r="H73" s="14">
+        <v>130</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="675" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB7210C-A999-4769-96E6-57B0CE6404B4}"/>
+  <xr:revisionPtr revIDLastSave="687" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C918EE3A-E51E-46AD-86D6-579D88C5311B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4256,26 +4256,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="14">
+        <v>720</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>340</v>
+      </c>
+      <c r="E74" s="14">
+        <v>150</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>150</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="687" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C918EE3A-E51E-46AD-86D6-579D88C5311B}"/>
+  <xr:revisionPtr revIDLastSave="701" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09357C91-B129-4738-ACD1-5CA58AAE6434}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>today learn join in DBMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday </t>
   </si>
 </sst>
 </file>
@@ -4302,26 +4305,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="14">
+        <v>700</v>
+      </c>
+      <c r="C75" s="14">
+        <v>25</v>
+      </c>
+      <c r="D75" s="14">
+        <v>320</v>
+      </c>
+      <c r="E75" s="14">
+        <v>120</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>200</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1365</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="701" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09357C91-B129-4738-ACD1-5CA58AAE6434}"/>
+  <xr:revisionPtr revIDLastSave="714" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AE338B7-AEA1-456B-858C-EE917CA1DEFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sunday </t>
+  </si>
+  <si>
+    <t>star making c1 minor project c++</t>
   </si>
 </sst>
 </file>
@@ -4351,26 +4354,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B76" s="14">
+        <v>681</v>
+      </c>
+      <c r="C76" s="14">
+        <v>30</v>
+      </c>
+      <c r="D76" s="14">
+        <v>340</v>
+      </c>
+      <c r="E76" s="14">
+        <v>60</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>250</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1361</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="714" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AE338B7-AEA1-456B-858C-EE917CA1DEFD}"/>
+  <xr:revisionPtr revIDLastSave="727" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A651F04-3D05-47E1-A277-84C50D75C263}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>star making c1 minor project c++</t>
+  </si>
+  <si>
+    <t>create minor project c++</t>
   </si>
 </sst>
 </file>
@@ -4400,26 +4403,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B77" s="14">
+        <v>650</v>
+      </c>
+      <c r="C77" s="14">
+        <v>20</v>
+      </c>
+      <c r="D77" s="14">
+        <v>120</v>
+      </c>
+      <c r="E77" s="14">
+        <v>90</v>
+      </c>
+      <c r="F77" s="14">
+        <v>350</v>
+      </c>
+      <c r="G77" s="14">
+        <v>7</v>
+      </c>
+      <c r="H77" s="14">
+        <v>180</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="727" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A651F04-3D05-47E1-A277-84C50D75C263}"/>
+  <xr:revisionPtr revIDLastSave="743" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EABD5038-DB4B-4E32-A417-A9A3E0367983}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B76" s="14">
         <v>681</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="B77" s="14">
         <v>650</v>
@@ -4449,26 +4449,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="14">
+        <v>700</v>
+      </c>
+      <c r="C78" s="14">
+        <v>30</v>
+      </c>
+      <c r="D78" s="14">
+        <v>160</v>
+      </c>
+      <c r="E78" s="14">
+        <v>60</v>
+      </c>
+      <c r="F78" s="14">
+        <v>200</v>
+      </c>
+      <c r="G78" s="14">
+        <v>4</v>
+      </c>
+      <c r="H78" s="14">
+        <v>220</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>

--- a/12600360.xlsx
+++ b/12600360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae48c435e1ea0692/Desktop/776/12600360/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="743" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EABD5038-DB4B-4E32-A417-A9A3E0367983}"/>
+  <xr:revisionPtr revIDLastSave="755" documentId="8_{0714D6D0-C0E6-4570-B139-85828D0C1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC80ADD8-1A2C-4A6D-AD94-A481378F6943}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4495,26 +4495,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="14">
+        <v>720</v>
+      </c>
+      <c r="C79" s="14">
+        <v>20</v>
+      </c>
+      <c r="D79" s="14">
+        <v>120</v>
+      </c>
+      <c r="E79" s="14">
+        <v>70</v>
+      </c>
+      <c r="F79" s="14">
+        <v>350</v>
+      </c>
+      <c r="G79" s="14">
+        <v>7</v>
+      </c>
+      <c r="H79" s="14">
+        <v>160</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
